--- a/Submission/CU_eventos_completo.xlsx
+++ b/Submission/CU_eventos_completo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livejaverianaedu-my.sharepoint.com/personal/emperadorc_s_javeriana_edu_co/Documents/SEMESTRES/8to Semestre/Arqui Software/ArquiSoftware/Submission/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_754DEE3355F33D4CCDA5E9E71E3E738E9AEFA5A5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B225E574-E200-FC46-BDA9-AEB57CDEE081}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_754DEE3355F33D4CCDA5E9E71E3E738E9AEFA5A5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B1661CD-63D9-0A44-8E3B-A3E6DE2C230C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" firstSheet="20" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CU-001" sheetId="1" r:id="rId1"/>
@@ -45,17 +45,13 @@
     <sheet name="CU-030" sheetId="30" r:id="rId30"/>
     <sheet name="CU-031" sheetId="31" r:id="rId31"/>
     <sheet name="CU-032" sheetId="32" r:id="rId32"/>
-    <sheet name="CU1" sheetId="33" r:id="rId33"/>
-    <sheet name="CU2" sheetId="34" r:id="rId34"/>
-    <sheet name="CU3" sheetId="35" r:id="rId35"/>
-    <sheet name="CU4" sheetId="36" r:id="rId36"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="737">
   <si>
     <t>CU-005</t>
   </si>
@@ -3632,7 +3628,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="246">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4300,6 +4296,15 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -15213,7 +15218,7 @@
     <col min="2" max="2" width="10.83203125" style="39" customWidth="1"/>
     <col min="3" max="3" width="25" style="39" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="31.1640625" style="39" customWidth="1"/>
+    <col min="5" max="5" width="46.83203125" style="39" customWidth="1"/>
     <col min="6" max="9" width="10.83203125" style="39" customWidth="1"/>
     <col min="10" max="16384" width="10.83203125" style="39"/>
   </cols>
@@ -15407,21 +15412,21 @@
       <c r="A18" s="46">
         <v>1</v>
       </c>
-      <c r="B18" s="230" t="s">
+      <c r="B18" s="246" t="s">
         <v>725</v>
       </c>
-      <c r="C18" s="124"/>
+      <c r="C18" s="247"/>
       <c r="D18" s="45"/>
-      <c r="E18" s="44"/>
+      <c r="E18" s="248"/>
     </row>
     <row r="19" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="46"/>
-      <c r="B19" s="230"/>
-      <c r="C19" s="124"/>
+      <c r="B19" s="246"/>
+      <c r="C19" s="247"/>
       <c r="D19" s="45">
         <v>2</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="248" t="s">
         <v>726</v>
       </c>
     </row>
@@ -15429,65 +15434,65 @@
       <c r="A20" s="46">
         <v>3</v>
       </c>
-      <c r="B20" s="230" t="s">
+      <c r="B20" s="246" t="s">
         <v>727</v>
       </c>
-      <c r="C20" s="124"/>
+      <c r="C20" s="247"/>
       <c r="D20" s="45"/>
-      <c r="E20" s="44"/>
+      <c r="E20" s="248"/>
     </row>
     <row r="21" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="46"/>
-      <c r="B21" s="230"/>
-      <c r="C21" s="124"/>
+      <c r="B21" s="246"/>
+      <c r="C21" s="247"/>
       <c r="D21" s="45">
         <v>4</v>
       </c>
-      <c r="E21" s="44" t="s">
+      <c r="E21" s="248" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="46"/>
-      <c r="B22" s="230"/>
-      <c r="C22" s="124"/>
+      <c r="B22" s="246"/>
+      <c r="C22" s="247"/>
       <c r="D22" s="45">
         <v>5</v>
       </c>
-      <c r="E22" s="44" t="s">
+      <c r="E22" s="248" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="46">
         <v>6</v>
       </c>
-      <c r="B23" s="230" t="s">
+      <c r="B23" s="246" t="s">
         <v>730</v>
       </c>
-      <c r="C23" s="124"/>
+      <c r="C23" s="247"/>
       <c r="D23" s="45"/>
-      <c r="E23" s="44"/>
-    </row>
-    <row r="24" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="248"/>
+    </row>
+    <row r="24" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="46">
         <v>7</v>
       </c>
-      <c r="B24" s="230" t="s">
+      <c r="B24" s="246" t="s">
         <v>731</v>
       </c>
-      <c r="C24" s="124"/>
+      <c r="C24" s="247"/>
       <c r="D24" s="45"/>
-      <c r="E24" s="44"/>
-    </row>
-    <row r="25" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E24" s="248"/>
+    </row>
+    <row r="25" spans="1:5" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="46"/>
-      <c r="B25" s="230"/>
-      <c r="C25" s="124"/>
+      <c r="B25" s="246"/>
+      <c r="C25" s="247"/>
       <c r="D25" s="45">
         <v>8</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="248" t="s">
         <v>732</v>
       </c>
     </row>
@@ -15559,7 +15564,7 @@
       <c r="D33" s="136"/>
       <c r="E33" s="134"/>
     </row>
-    <row r="34" spans="1:5" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" ht="103" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="239" t="s">
         <v>68</v>
       </c>
@@ -15570,7 +15575,7 @@
       <c r="D34" s="136"/>
       <c r="E34" s="134"/>
     </row>
-    <row r="35" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="239" t="s">
         <v>70</v>
       </c>
@@ -15625,1637 +15630,6 @@
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="A16:E16"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.5" style="39" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="39" customWidth="1"/>
-    <col min="3" max="3" width="25" style="39" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" style="39" customWidth="1"/>
-    <col min="6" max="9" width="10.83203125" style="39" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="39"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="32.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="82" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="153" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="145"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="67"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-    </row>
-    <row r="3" spans="1:5" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="156" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="127"/>
-      <c r="D4" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="81">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="156" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="127"/>
-      <c r="D5" s="86" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="76" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-    </row>
-    <row r="7" spans="1:5" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="150" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="147"/>
-    </row>
-    <row r="8" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="144" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="145"/>
-      <c r="C8" s="143" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="127"/>
-      <c r="E8" s="124"/>
-    </row>
-    <row r="9" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="144" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="145"/>
-      <c r="C9" s="143" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="127"/>
-      <c r="E9" s="124"/>
-    </row>
-    <row r="10" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="145"/>
-      <c r="C10" s="143" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="127"/>
-      <c r="E10" s="124"/>
-    </row>
-    <row r="11" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="144" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="145"/>
-      <c r="C11" s="143" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="124"/>
-    </row>
-    <row r="12" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="144" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="145"/>
-      <c r="C12" s="143" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="124"/>
-    </row>
-    <row r="13" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="157" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="145"/>
-      <c r="C13" s="143" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="127"/>
-      <c r="E13" s="124"/>
-    </row>
-    <row r="14" spans="1:5" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="151" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="152"/>
-      <c r="C14" s="143" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="124"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="146" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="122"/>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="147"/>
-    </row>
-    <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="89" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="90" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52">
-        <v>1</v>
-      </c>
-      <c r="B18" s="142" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="77"/>
-    </row>
-    <row r="19" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52"/>
-      <c r="B19" s="142"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="49">
-        <v>2</v>
-      </c>
-      <c r="E19" s="77" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52">
-        <v>3</v>
-      </c>
-      <c r="B20" s="142" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="124"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="77"/>
-    </row>
-    <row r="21" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52"/>
-      <c r="B21" s="142"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="49">
-        <v>4</v>
-      </c>
-      <c r="E21" s="77" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52">
-        <v>5</v>
-      </c>
-      <c r="B22" s="142" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="124"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="77"/>
-    </row>
-    <row r="23" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="50"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="49">
-        <v>6</v>
-      </c>
-      <c r="E23" s="77" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="50"/>
-      <c r="B24" s="142"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="49">
-        <v>7</v>
-      </c>
-      <c r="E24" s="77" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="50"/>
-      <c r="B25" s="142"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="49">
-        <v>8</v>
-      </c>
-      <c r="E25" s="77" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41"/>
-      <c r="B26" s="155"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-    </row>
-    <row r="27" spans="1:5" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="149" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="147"/>
-      <c r="C27" s="143" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="127"/>
-      <c r="E27" s="124"/>
-    </row>
-    <row r="28" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="144" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="145"/>
-      <c r="C28" s="143" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="127"/>
-      <c r="E28" s="124"/>
-    </row>
-    <row r="29" spans="1:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="151" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="152"/>
-      <c r="C29" s="143" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="124"/>
-    </row>
-    <row r="30" spans="1:5" ht="133" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="141"/>
-      <c r="C30" s="143" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="124"/>
-    </row>
-    <row r="31" spans="1:5" ht="109" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="140" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="141"/>
-      <c r="C31" s="143" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="127"/>
-      <c r="E31" s="124"/>
-    </row>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="A31:B31"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
-  <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.5" style="39" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="39" customWidth="1"/>
-    <col min="3" max="3" width="25" style="39" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="44.5" style="39" customWidth="1"/>
-    <col min="6" max="9" width="10.83203125" style="39" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="39"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="32.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="82" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="163" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="124"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="67"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-    </row>
-    <row r="3" spans="1:5" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="143" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="80">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="143" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="86" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="75" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-    </row>
-    <row r="7" spans="1:5" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="160" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="130"/>
-    </row>
-    <row r="8" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="158" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="143" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="127"/>
-      <c r="E8" s="124"/>
-    </row>
-    <row r="9" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="158" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="124"/>
-      <c r="C9" s="143" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="127"/>
-      <c r="E9" s="124"/>
-    </row>
-    <row r="10" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="143" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="127"/>
-      <c r="E10" s="124"/>
-    </row>
-    <row r="11" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="158" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="124"/>
-      <c r="C11" s="143" t="s">
-        <v>77</v>
-      </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="124"/>
-    </row>
-    <row r="12" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="124"/>
-      <c r="C12" s="143" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="124"/>
-    </row>
-    <row r="13" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="165" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="124"/>
-      <c r="C13" s="143" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="127"/>
-      <c r="E13" s="124"/>
-    </row>
-    <row r="14" spans="1:5" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="134"/>
-      <c r="C14" s="143" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="124"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="159" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="130"/>
-    </row>
-    <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="89" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="90" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52">
-        <v>1</v>
-      </c>
-      <c r="B18" s="142" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="77"/>
-    </row>
-    <row r="19" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52"/>
-      <c r="B19" s="142"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="49">
-        <v>2</v>
-      </c>
-      <c r="E19" s="77" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52"/>
-      <c r="B20" s="142"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="49">
-        <v>3</v>
-      </c>
-      <c r="E20" s="77" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52"/>
-      <c r="B21" s="142"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="49">
-        <v>4</v>
-      </c>
-      <c r="E21" s="77" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="49">
-        <v>5</v>
-      </c>
-      <c r="E22" s="77" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="49">
-        <v>6</v>
-      </c>
-      <c r="E23" s="77" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="52"/>
-      <c r="B24" s="142"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="49">
-        <v>7</v>
-      </c>
-      <c r="E24" s="77" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="52"/>
-      <c r="B25" s="142"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="49">
-        <v>8</v>
-      </c>
-      <c r="E25" s="77" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="52">
-        <v>9</v>
-      </c>
-      <c r="B26" s="142" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="124"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="77"/>
-    </row>
-    <row r="27" spans="1:5" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="52"/>
-      <c r="B27" s="143"/>
-      <c r="C27" s="124"/>
-      <c r="D27" s="49">
-        <v>10</v>
-      </c>
-      <c r="E27" s="77" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="41"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-    </row>
-    <row r="29" spans="1:5" ht="113" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="164" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="130"/>
-      <c r="C29" s="143" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="124"/>
-    </row>
-    <row r="30" spans="1:5" ht="73" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="158" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="124"/>
-      <c r="C30" s="143" t="s">
-        <v>92</v>
-      </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="124"/>
-    </row>
-    <row r="31" spans="1:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="162" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="134"/>
-      <c r="C31" s="143" t="s">
-        <v>67</v>
-      </c>
-      <c r="D31" s="127"/>
-      <c r="E31" s="124"/>
-    </row>
-    <row r="32" spans="1:5" ht="107" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="161" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="134"/>
-      <c r="C32" s="143" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" s="127"/>
-      <c r="E32" s="124"/>
-    </row>
-    <row r="33" spans="1:5" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="161" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="134"/>
-      <c r="C33" s="143" t="s">
-        <v>94</v>
-      </c>
-      <c r="D33" s="127"/>
-      <c r="E33" s="124"/>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A11:B11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.5" style="39" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="39" customWidth="1"/>
-    <col min="3" max="3" width="25" style="39" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="48" style="39" customWidth="1"/>
-    <col min="6" max="9" width="10.83203125" style="39" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="39"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="32.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="82" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="163" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="124"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="67"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-    </row>
-    <row r="3" spans="1:5" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="143" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="80">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="143" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="86" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="75" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="75"/>
-    </row>
-    <row r="7" spans="1:5" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="160" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="130"/>
-    </row>
-    <row r="8" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="158" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="143" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="127"/>
-      <c r="E8" s="124"/>
-    </row>
-    <row r="9" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="158" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="124"/>
-      <c r="C9" s="143" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="127"/>
-      <c r="E9" s="124"/>
-    </row>
-    <row r="10" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="143" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="127"/>
-      <c r="E10" s="124"/>
-    </row>
-    <row r="11" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="158" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="124"/>
-      <c r="C11" s="143" t="s">
-        <v>98</v>
-      </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="124"/>
-    </row>
-    <row r="12" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="124"/>
-      <c r="C12" s="143" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="124"/>
-    </row>
-    <row r="13" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="165" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="124"/>
-      <c r="C13" s="143" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="127"/>
-      <c r="E13" s="124"/>
-    </row>
-    <row r="14" spans="1:5" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="134"/>
-      <c r="C14" s="143" t="s">
-        <v>101</v>
-      </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="124"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="159" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="130"/>
-    </row>
-    <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="89" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="90" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52">
-        <v>1</v>
-      </c>
-      <c r="B18" s="142" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="77"/>
-    </row>
-    <row r="19" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52"/>
-      <c r="B19" s="142"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="49">
-        <v>2</v>
-      </c>
-      <c r="E19" s="77" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52"/>
-      <c r="B20" s="142"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="49">
-        <v>3</v>
-      </c>
-      <c r="E20" s="77" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52"/>
-      <c r="B21" s="142"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="49">
-        <v>4</v>
-      </c>
-      <c r="E21" s="77" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52">
-        <v>5</v>
-      </c>
-      <c r="B22" s="142" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="124"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="77"/>
-    </row>
-    <row r="23" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="49">
-        <v>6</v>
-      </c>
-      <c r="E23" s="77" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="52"/>
-      <c r="B24" s="142"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="49">
-        <v>7</v>
-      </c>
-      <c r="E24" s="77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="52"/>
-      <c r="B25" s="142"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="49">
-        <v>8</v>
-      </c>
-      <c r="E25" s="77" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="78"/>
-      <c r="B26" s="168"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="70">
-        <v>9</v>
-      </c>
-      <c r="E26" s="79" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="166"/>
-      <c r="C27" s="167"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="40"/>
-    </row>
-    <row r="28" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="164" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="130"/>
-      <c r="C28" s="143" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" s="127"/>
-      <c r="E28" s="124"/>
-    </row>
-    <row r="29" spans="1:5" ht="61" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="158" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="124"/>
-      <c r="C29" s="143" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="124"/>
-    </row>
-    <row r="30" spans="1:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="162" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="134"/>
-      <c r="C30" s="143" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="124"/>
-    </row>
-    <row r="31" spans="1:5" ht="76" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="161" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="134"/>
-      <c r="C31" s="143" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" s="127"/>
-      <c r="E31" s="124"/>
-    </row>
-    <row r="32" spans="1:5" ht="65" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="161" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="134"/>
-      <c r="C32" s="143" t="s">
-        <v>114</v>
-      </c>
-      <c r="D32" s="127"/>
-      <c r="E32" s="124"/>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A11:B11"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.33203125" style="39" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" style="39" customWidth="1"/>
-    <col min="3" max="3" width="27.83203125" style="39" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="39" customWidth="1"/>
-    <col min="5" max="5" width="42.83203125" style="39" customWidth="1"/>
-    <col min="6" max="9" width="10.83203125" style="39" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="39"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="32.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="82" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="163" t="s">
-        <v>116</v>
-      </c>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="124"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="67"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-    </row>
-    <row r="3" spans="1:5" ht="14.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="143" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="80">
-        <v>46247</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="143" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="124"/>
-      <c r="D5" s="86" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="75" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-    </row>
-    <row r="7" spans="1:5" ht="17.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="87" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="85" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="150" t="s">
-        <v>116</v>
-      </c>
-      <c r="E7" s="147"/>
-    </row>
-    <row r="8" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="158" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="143" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" s="127"/>
-      <c r="E8" s="124"/>
-    </row>
-    <row r="9" spans="1:5" ht="31" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="158" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="124"/>
-      <c r="C9" s="143" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="127"/>
-      <c r="E9" s="124"/>
-    </row>
-    <row r="10" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="124"/>
-      <c r="C10" s="143" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="127"/>
-      <c r="E10" s="124"/>
-    </row>
-    <row r="11" spans="1:5" ht="23" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="158" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="124"/>
-      <c r="C11" s="143" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="127"/>
-      <c r="E11" s="124"/>
-    </row>
-    <row r="12" spans="1:5" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="158" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="124"/>
-      <c r="C12" s="143" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="127"/>
-      <c r="E12" s="124"/>
-    </row>
-    <row r="13" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="165" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="124"/>
-      <c r="C13" s="143" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" s="127"/>
-      <c r="E13" s="124"/>
-    </row>
-    <row r="14" spans="1:5" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="162" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="134"/>
-      <c r="C14" s="143" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="127"/>
-      <c r="E14" s="124"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="41"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="159" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="129"/>
-      <c r="C16" s="129"/>
-      <c r="D16" s="129"/>
-      <c r="E16" s="130"/>
-    </row>
-    <row r="17" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="148" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="89" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17" s="90" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="52">
-        <v>1</v>
-      </c>
-      <c r="B18" s="142" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="124"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="77"/>
-    </row>
-    <row r="19" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="52"/>
-      <c r="B19" s="142"/>
-      <c r="C19" s="124"/>
-      <c r="D19" s="49">
-        <v>2</v>
-      </c>
-      <c r="E19" s="77" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="52"/>
-      <c r="B20" s="142"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="49">
-        <v>3</v>
-      </c>
-      <c r="E20" s="77" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="52"/>
-      <c r="B21" s="142"/>
-      <c r="C21" s="124"/>
-      <c r="D21" s="49">
-        <v>4</v>
-      </c>
-      <c r="E21" s="77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="52"/>
-      <c r="B22" s="142"/>
-      <c r="C22" s="124"/>
-      <c r="D22" s="49">
-        <v>5</v>
-      </c>
-      <c r="E22" s="77" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="52"/>
-      <c r="B23" s="142"/>
-      <c r="C23" s="124"/>
-      <c r="D23" s="49">
-        <v>6</v>
-      </c>
-      <c r="E23" s="77" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="52"/>
-      <c r="B24" s="142"/>
-      <c r="C24" s="124"/>
-      <c r="D24" s="49">
-        <v>7</v>
-      </c>
-      <c r="E24" s="77" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="52"/>
-      <c r="B25" s="142"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="49">
-        <v>8</v>
-      </c>
-      <c r="E25" s="77" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="41" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="78">
-        <v>9</v>
-      </c>
-      <c r="B26" s="168" t="s">
-        <v>130</v>
-      </c>
-      <c r="C26" s="134"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="79"/>
-    </row>
-    <row r="27" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="91"/>
-      <c r="B27" s="169"/>
-      <c r="C27" s="170"/>
-      <c r="D27" s="92"/>
-      <c r="E27" s="92"/>
-    </row>
-    <row r="28" spans="1:5" ht="70" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="176" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="174"/>
-      <c r="C28" s="172" t="s">
-        <v>131</v>
-      </c>
-      <c r="D28" s="173"/>
-      <c r="E28" s="174"/>
-    </row>
-    <row r="29" spans="1:5" ht="57" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="158" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="124"/>
-      <c r="C29" s="143" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="127"/>
-      <c r="E29" s="124"/>
-    </row>
-    <row r="30" spans="1:5" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="162" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="134"/>
-      <c r="C30" s="143" t="s">
-        <v>67</v>
-      </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="124"/>
-    </row>
-    <row r="31" spans="1:5" ht="65" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="161" t="s">
-        <v>68</v>
-      </c>
-      <c r="B31" s="134"/>
-      <c r="C31" s="143" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" s="127"/>
-      <c r="E31" s="124"/>
-    </row>
-    <row r="32" spans="1:5" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="175" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="152"/>
-      <c r="C32" s="171" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="136"/>
-      <c r="E32" s="134"/>
-    </row>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="A11:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
